--- a/excel outputs/דוח נכסים לתאריך:24-07-2026.xlsx
+++ b/excel outputs/דוח נכסים לתאריך:24-07-2026.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="נכסים חשודים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="דוח עסקים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'נכסים חשודים'!$A$1:$G$13</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,18 +31,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000563C1"/>
-      <sz val="10"/>
-      <u val="single"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -54,16 +42,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,22 +71,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,19 +441,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>שם העסק</t>
@@ -523,371 +489,8 @@
           <t>קישור 3</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>גרינברג-אסמעיל, משרד עורכי דין</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>דב גרונר 12, ירושלים</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>עורכי דין</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.t.co.il/Business/Card-686089.html</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>גורי ששון - ניהול חשבונות</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>דב גרונר 12, ירושלים</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>הנהלת חשבונות</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.b144.co.il/b144_sip/401C0413417264544D170214/</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>עמיגור דיור מוגן תלפיות</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>דב גרונר 17, ירושלים</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>דיור מוגן</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>https://easy.co.il/page/26254766</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>קואופ שופ</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>דב גרונר 22, ירושלים</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>סופרמרקט</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/5553910/35760/</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ניבי פיתוח קול וגיטרות</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>דב גרונר 26, ירושלים</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>פיתוח קול ושיעורי גיטרה</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/80112073/39740/</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ארמון הנציב – בית מרקחת</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>דב גרונר 3, ירושלים</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>בית מרקחת</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/15385600/8150/</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>ד"ר ביאטריס שוקרון</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>דב גרונר 5, ירושלים</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>רופאת משפחה</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/80221146/46210/</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>לרר משה – מורה לנהיגה</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>דב גרונר 7, ירושלים</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>מורה לנהיגה</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/75772650/8450/</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>חלק ממני</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>מאיר גרוסמן 16, ירושלים</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>חנות עודפים לחשמל</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/80273691/16870/</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>אחים מאיר ושות'</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>מאיר גרוסמן 22, ירושלים</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>זיפות גגות</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/4018360/9200/</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>הוצאות איי.אי.אל</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>פנחס גרייבסקי 6, גבעת שאול, ירושלים</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>הוצאה לאור</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/26495490/13410/</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>יוקרה – רקמת בוטיק</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>גרינברג חיים 5, ירושלים</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>רקמה ויודאיקה</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.b144.co.il/b144_sip/401D0D1A4370655D4D1D0D1145/</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>